--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D2">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="E2">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>161</v>
       </c>
       <c r="D3">
-        <v>112</v>
+        <v>264</v>
       </c>
       <c r="E3">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D3">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>426</v>
